--- a/wishlist_test_report.xlsx
+++ b/wishlist_test_report.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="23">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -35,7 +35,7 @@
     <t>Note</t>
   </si>
   <si>
-    <t>TC_01</t>
+    <t>TC_WL_01</t>
   </si>
   <si>
     <t>customer_binh</t>
@@ -47,13 +47,64 @@
     <t>Hạng Nhất</t>
   </si>
   <si>
-    <t>PASS</t>
-  </si>
-  <si>
-    <t>73621</t>
-  </si>
-  <si>
-    <t>Thêm phòng vào wishlist thành công thông qua UI.</t>
+    <t>FAIL</t>
+  </si>
+  <si>
+    <t>62646</t>
+  </si>
+  <si>
+    <t>Error: Expected condition failed: waiting for element found by By.xpath: //div[contains(@class, 'hotel-card') and .//h5[contains(@class, 'card-title') and contains(text(), 'Hotel Test 1')]]/descendant::a[contains(@class, 'custom-hl-view-btn')] to be clickable, but the element was not found: org.openqa.selenium.NoSuchElementException: no such element: Unable to locate element: {"method":"xpath","selector":"//div[contains(@class, 'hotel-card') and .//h5[contains(@class, 'card-title') and contains(text(), 'Hotel Test 1')]]/descendant::a[contains(@class, 'custom-hl-view-btn')]"}.
+(tried for 15 seconds with 500 milliseconds interval)
+Build info: version: '4.43.0', revision: 'dd0f534'
+System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '25.0.2'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 150.0.7871.102, chrome: {chromedriverVersion: 150.0.7871.115 (25f5b661e5b..., userDataDir: C:\Users\luuhu\AppData\Loca...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:52023}, goog:processID: 7752, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:52023/devtoo..., se:cdpVersion: 150.0.7871.102, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: c4bf3122ac13fd9b35d102114285829e</t>
+  </si>
+  <si>
+    <t>TC_WL_02</t>
+  </si>
+  <si>
+    <t>25153</t>
+  </si>
+  <si>
+    <t>Error: Expected condition failed: waiting for element found by By.xpath: //div[contains(@class, 'hotel-card') and .//h5[contains(@class, 'card-title') and contains(text(), 'Hotel Test 1')]]/descendant::a[contains(@class, 'custom-hl-view-btn')] to be clickable, but the element was not found: org.openqa.selenium.NoSuchElementException: no such element: Unable to locate element: {"method":"xpath","selector":"//div[contains(@class, 'hotel-card') and .//h5[contains(@class, 'card-title') and contains(text(), 'Hotel Test 1')]]/descendant::a[contains(@class, 'custom-hl-view-btn')]"}.
+(tried for 15 seconds with 500 milliseconds interval)
+Build info: version: '4.43.0', revision: 'dd0f534'
+System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '25.0.2'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 150.0.7871.102, chrome: {chromedriverVersion: 150.0.7871.115 (25f5b661e5b..., userDataDir: C:\Users\luuhu\AppData\Loca...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:55124}, goog:processID: 3076, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:55124/devtoo..., se:cdpVersion: 150.0.7871.102, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 5d1ff02719e057cd807f6e829c945c07</t>
+  </si>
+  <si>
+    <t>TC_WL_03</t>
+  </si>
+  <si>
+    <t>25205</t>
+  </si>
+  <si>
+    <t>Error: Expected condition failed: waiting for element found by By.xpath: //div[contains(@class, 'hotel-card') and .//h5[contains(@class, 'card-title') and contains(text(), 'Hotel Test 1')]]/descendant::a[contains(@class, 'custom-hl-view-btn')] to be clickable, but the element was not found: org.openqa.selenium.NoSuchElementException: no such element: Unable to locate element: {"method":"xpath","selector":"//div[contains(@class, 'hotel-card') and .//h5[contains(@class, 'card-title') and contains(text(), 'Hotel Test 1')]]/descendant::a[contains(@class, 'custom-hl-view-btn')]"}.
+(tried for 15 seconds with 500 milliseconds interval)
+Build info: version: '4.43.0', revision: 'dd0f534'
+System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '25.0.2'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 150.0.7871.102, chrome: {chromedriverVersion: 150.0.7871.115 (25f5b661e5b..., userDataDir: C:\Users\luuhu\AppData\Loca...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:63621}, goog:processID: 2964, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:63621/devtoo..., se:cdpVersion: 150.0.7871.102, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: b6a51e797b31ebda90c8324987538293</t>
+  </si>
+  <si>
+    <t>TC_WL_04</t>
+  </si>
+  <si>
+    <t>22373</t>
+  </si>
+  <si>
+    <t>Error: Expected condition failed: waiting for element found by By.xpath: //div[contains(@class, 'hotel-card') and .//h5[contains(@class, 'card-title') and contains(text(), 'Hotel Test 1')]]/descendant::a[contains(@class, 'custom-hl-view-btn')] to be clickable, but the element was not found: org.openqa.selenium.NoSuchElementException: no such element: Unable to locate element: {"method":"xpath","selector":"//div[contains(@class, 'hotel-card') and .//h5[contains(@class, 'card-title') and contains(text(), 'Hotel Test 1')]]/descendant::a[contains(@class, 'custom-hl-view-btn')]"}.
+(tried for 15 seconds with 500 milliseconds interval)
+Build info: version: '4.43.0', revision: 'dd0f534'
+System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '25.0.2'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 150.0.7871.102, chrome: {chromedriverVersion: 150.0.7871.115 (25f5b661e5b..., userDataDir: C:\Users\luuhu\AppData\Loca...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:65266}, goog:processID: 18808, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:65266/devtoo..., se:cdpVersion: 150.0.7871.102, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 8f1eacac202a269dc15466ffd457a2b3</t>
   </si>
 </sst>
 </file>
@@ -131,7 +182,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="10.84765625" customWidth="true" bestFit="true"/>
@@ -140,7 +191,7 @@
     <col min="4" max="4" width="10.1953125" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="6.06640625" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="17.5546875" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="41.55859375" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="255.0" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -179,7 +230,7 @@
       <c r="D2" t="s" s="0">
         <v>10</v>
       </c>
-      <c r="E2" t="s" s="2">
+      <c r="E2" t="s" s="3">
         <v>11</v>
       </c>
       <c r="F2" t="s" s="0">
@@ -187,6 +238,75 @@
       </c>
       <c r="G2" t="s" s="0">
         <v>13</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="E3" t="s" s="3">
+        <v>11</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="E4" t="s" s="3">
+        <v>11</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="E5" t="s" s="3">
+        <v>11</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/wishlist_test_report.xlsx
+++ b/wishlist_test_report.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="30">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -26,6 +26,9 @@
     <t>Room Type</t>
   </si>
   <si>
+    <t>Description</t>
+  </si>
+  <si>
     <t>Status</t>
   </si>
   <si>
@@ -41,70 +44,64 @@
     <t>customer_binh</t>
   </si>
   <si>
-    <t>Hotel Test 1</t>
-  </si>
-  <si>
-    <t>Hạng Nhất</t>
-  </si>
-  <si>
-    <t>FAIL</t>
-  </si>
-  <si>
-    <t>62646</t>
-  </si>
-  <si>
-    <t>Error: Expected condition failed: waiting for element found by By.xpath: //div[contains(@class, 'hotel-card') and .//h5[contains(@class, 'card-title') and contains(text(), 'Hotel Test 1')]]/descendant::a[contains(@class, 'custom-hl-view-btn')] to be clickable, but the element was not found: org.openqa.selenium.NoSuchElementException: no such element: Unable to locate element: {"method":"xpath","selector":"//div[contains(@class, 'hotel-card') and .//h5[contains(@class, 'card-title') and contains(text(), 'Hotel Test 1')]]/descendant::a[contains(@class, 'custom-hl-view-btn')]"}.
-(tried for 15 seconds with 500 milliseconds interval)
-Build info: version: '4.43.0', revision: 'dd0f534'
-System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '25.0.2'
-Driver info: org.openqa.selenium.chrome.ChromeDriver
-Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 150.0.7871.102, chrome: {chromedriverVersion: 150.0.7871.115 (25f5b661e5b..., userDataDir: C:\Users\luuhu\AppData\Loca...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:52023}, goog:processID: 7752, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:52023/devtoo..., se:cdpVersion: 150.0.7871.102, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
-Session ID: c4bf3122ac13fd9b35d102114285829e</t>
+    <t>Vinpearl Resort Nha Trang</t>
+  </si>
+  <si>
+    <t>Deluxe Sea View</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>PASS</t>
+  </si>
+  <si>
+    <t>9680</t>
+  </si>
+  <si>
+    <t>Successfully added room to wishlist and verified on Wishlist page.</t>
   </si>
   <si>
     <t>TC_WL_02</t>
   </si>
   <si>
-    <t>25153</t>
-  </si>
-  <si>
-    <t>Error: Expected condition failed: waiting for element found by By.xpath: //div[contains(@class, 'hotel-card') and .//h5[contains(@class, 'card-title') and contains(text(), 'Hotel Test 1')]]/descendant::a[contains(@class, 'custom-hl-view-btn')] to be clickable, but the element was not found: org.openqa.selenium.NoSuchElementException: no such element: Unable to locate element: {"method":"xpath","selector":"//div[contains(@class, 'hotel-card') and .//h5[contains(@class, 'card-title') and contains(text(), 'Hotel Test 1')]]/descendant::a[contains(@class, 'custom-hl-view-btn')]"}.
-(tried for 15 seconds with 500 milliseconds interval)
-Build info: version: '4.43.0', revision: 'dd0f534'
-System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '25.0.2'
-Driver info: org.openqa.selenium.chrome.ChromeDriver
-Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 150.0.7871.102, chrome: {chromedriverVersion: 150.0.7871.115 (25f5b661e5b..., userDataDir: C:\Users\luuhu\AppData\Loca...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:55124}, goog:processID: 3076, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:55124/devtoo..., se:cdpVersion: 150.0.7871.102, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
-Session ID: 5d1ff02719e057cd807f6e829c945c07</t>
+    <t>Family Garden View</t>
+  </si>
+  <si>
+    <t>4114</t>
+  </si>
+  <si>
+    <t>Successfully removed room from wishlist via toggle on Rooms page.</t>
   </si>
   <si>
     <t>TC_WL_03</t>
   </si>
   <si>
-    <t>25205</t>
-  </si>
-  <si>
-    <t>Error: Expected condition failed: waiting for element found by By.xpath: //div[contains(@class, 'hotel-card') and .//h5[contains(@class, 'card-title') and contains(text(), 'Hotel Test 1')]]/descendant::a[contains(@class, 'custom-hl-view-btn')] to be clickable, but the element was not found: org.openqa.selenium.NoSuchElementException: no such element: Unable to locate element: {"method":"xpath","selector":"//div[contains(@class, 'hotel-card') and .//h5[contains(@class, 'card-title') and contains(text(), 'Hotel Test 1')]]/descendant::a[contains(@class, 'custom-hl-view-btn')]"}.
-(tried for 15 seconds with 500 milliseconds interval)
-Build info: version: '4.43.0', revision: 'dd0f534'
-System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '25.0.2'
-Driver info: org.openqa.selenium.chrome.ChromeDriver
-Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 150.0.7871.102, chrome: {chromedriverVersion: 150.0.7871.115 (25f5b661e5b..., userDataDir: C:\Users\luuhu\AppData\Loca...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:63621}, goog:processID: 2964, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:63621/devtoo..., se:cdpVersion: 150.0.7871.102, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
-Session ID: b6a51e797b31ebda90c8324987538293</t>
+    <t>InterContinental Danang Sun Peninsula Resort</t>
+  </si>
+  <si>
+    <t>Resort King Room</t>
+  </si>
+  <si>
+    <t>4506</t>
+  </si>
+  <si>
+    <t>Successfully removed room from wishlist via red heart button on Wishlist page.</t>
   </si>
   <si>
     <t>TC_WL_04</t>
   </si>
   <si>
-    <t>22373</t>
-  </si>
-  <si>
-    <t>Error: Expected condition failed: waiting for element found by By.xpath: //div[contains(@class, 'hotel-card') and .//h5[contains(@class, 'card-title') and contains(text(), 'Hotel Test 1')]]/descendant::a[contains(@class, 'custom-hl-view-btn')] to be clickable, but the element was not found: org.openqa.selenium.NoSuchElementException: no such element: Unable to locate element: {"method":"xpath","selector":"//div[contains(@class, 'hotel-card') and .//h5[contains(@class, 'card-title') and contains(text(), 'Hotel Test 1')]]/descendant::a[contains(@class, 'custom-hl-view-btn')]"}.
-(tried for 15 seconds with 500 milliseconds interval)
-Build info: version: '4.43.0', revision: 'dd0f534'
-System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '25.0.2'
-Driver info: org.openqa.selenium.chrome.ChromeDriver
-Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 150.0.7871.102, chrome: {chromedriverVersion: 150.0.7871.115 (25f5b661e5b..., userDataDir: C:\Users\luuhu\AppData\Loca...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:65266}, goog:processID: 18808, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:65266/devtoo..., se:cdpVersion: 150.0.7871.102, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
-Session ID: 8f1eacac202a269dc15466ffd457a2b3</t>
+    <t>Four Seasons Resort The Nam Hai</t>
+  </si>
+  <si>
+    <t>Deluxe Beach Front</t>
+  </si>
+  <si>
+    <t>12736</t>
+  </si>
+  <si>
+    <t>Successfully verified that unauthorized users cannot see the wishlist heart button.</t>
   </si>
 </sst>
 </file>
@@ -182,16 +179,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="10.84765625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="13.06640625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="10.734375" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="10.1953125" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="6.06640625" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="17.5546875" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="37.96875" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="16.9453125" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="10.328125" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="6.06640625" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="17.5546875" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="66.59765625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -216,97 +214,112 @@
       <c r="G1" t="s" s="1">
         <v>6</v>
       </c>
+      <c r="H1" t="s" s="1">
+        <v>7</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="E2" t="s" s="3">
         <v>11</v>
       </c>
-      <c r="F2" t="s" s="0">
+      <c r="E2" t="s" s="0">
         <v>12</v>
       </c>
+      <c r="F2" t="s" s="2">
+        <v>13</v>
+      </c>
       <c r="G2" t="s" s="0">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>15</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="E3" t="s" s="3">
-        <v>11</v>
-      </c>
-      <c r="F3" t="s" s="0">
-        <v>15</v>
+        <v>17</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s" s="2">
+        <v>13</v>
       </c>
       <c r="G3" t="s" s="0">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>19</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="E4" t="s" s="3">
-        <v>11</v>
-      </c>
-      <c r="F4" t="s" s="0">
-        <v>18</v>
+        <v>22</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F4" t="s" s="2">
+        <v>13</v>
       </c>
       <c r="G4" t="s" s="0">
-        <v>19</v>
+        <v>23</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>24</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="E5" t="s" s="3">
-        <v>11</v>
-      </c>
-      <c r="F5" t="s" s="0">
-        <v>21</v>
+        <v>27</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F5" t="s" s="2">
+        <v>13</v>
       </c>
       <c r="G5" t="s" s="0">
-        <v>22</v>
+        <v>28</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/wishlist_test_report.xlsx
+++ b/wishlist_test_report.xlsx
@@ -44,64 +44,84 @@
     <t>customer_binh</t>
   </si>
   <si>
-    <t>Vinpearl Resort Nha Trang</t>
-  </si>
-  <si>
-    <t>Deluxe Sea View</t>
+    <t>Thảo Điểm</t>
+  </si>
+  <si>
+    <t>Deluxe Room</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>PASS</t>
-  </si>
-  <si>
-    <t>9680</t>
-  </si>
-  <si>
-    <t>Successfully added room to wishlist and verified on Wishlist page.</t>
+    <t>FAIL</t>
+  </si>
+  <si>
+    <t>24355</t>
+  </si>
+  <si>
+    <t>Error: Expected condition failed: waiting for visibility of element located by By.id: avatarBtn (tried for 15 second(s) with 500 milliseconds interval)
+Build info: version: '4.31.0', revision: '1ef9f18787*'
+System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '21.0.8'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 150.0.7871.115, chrome: {chromedriverVersion: 150.0.7871.124 (9261fd0a595..., userDataDir: C:\Users\luuhu\AppData\Loca...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:56249}, goog:processID: 11112, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:56249/devtoo..., se:cdpVersion: 150.0.7871.115, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: a208539ecdd1c2b36bb2548fade1987a</t>
   </si>
   <si>
     <t>TC_WL_02</t>
   </si>
   <si>
-    <t>Family Garden View</t>
-  </si>
-  <si>
-    <t>4114</t>
-  </si>
-  <si>
-    <t>Successfully removed room from wishlist via toggle on Rooms page.</t>
+    <t>Standard Room</t>
+  </si>
+  <si>
+    <t>23226</t>
+  </si>
+  <si>
+    <t>Error: Expected condition failed: waiting for visibility of element located by By.id: avatarBtn (tried for 15 second(s) with 500 milliseconds interval)
+Build info: version: '4.31.0', revision: '1ef9f18787*'
+System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '21.0.8'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 150.0.7871.115, chrome: {chromedriverVersion: 150.0.7871.124 (9261fd0a595..., userDataDir: C:\Users\luuhu\AppData\Loca...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:49964}, goog:processID: 1992, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:49964/devtoo..., se:cdpVersion: 150.0.7871.115, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: e397e013085ad590c2ab14d06a5bb636</t>
   </si>
   <si>
     <t>TC_WL_03</t>
   </si>
   <si>
-    <t>InterContinental Danang Sun Peninsula Resort</t>
-  </si>
-  <si>
-    <t>Resort King Room</t>
-  </si>
-  <si>
-    <t>4506</t>
-  </si>
-  <si>
-    <t>Successfully removed room from wishlist via red heart button on Wishlist page.</t>
+    <t>Sun Hotel</t>
+  </si>
+  <si>
+    <t>Double Room</t>
+  </si>
+  <si>
+    <t>23093</t>
+  </si>
+  <si>
+    <t>Error: Expected condition failed: waiting for visibility of element located by By.id: avatarBtn (tried for 15 second(s) with 500 milliseconds interval)
+Build info: version: '4.31.0', revision: '1ef9f18787*'
+System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '21.0.8'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 150.0.7871.115, chrome: {chromedriverVersion: 150.0.7871.124 (9261fd0a595..., userDataDir: C:\Users\luuhu\AppData\Loca...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:60224}, goog:processID: 496, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:60224/devtoo..., se:cdpVersion: 150.0.7871.115, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: cc7e24a984b03dd3e84129720cca31e8</t>
   </si>
   <si>
     <t>TC_WL_04</t>
   </si>
   <si>
-    <t>Four Seasons Resort The Nam Hai</t>
-  </si>
-  <si>
-    <t>Deluxe Beach Front</t>
-  </si>
-  <si>
-    <t>12736</t>
-  </si>
-  <si>
-    <t>Successfully verified that unauthorized users cannot see the wishlist heart button.</t>
+    <t>Rose Boutique</t>
+  </si>
+  <si>
+    <t>Rose Boutique Suite</t>
+  </si>
+  <si>
+    <t>23985</t>
+  </si>
+  <si>
+    <t>Error: Expected condition failed: waiting for element to be clickable: By.xpath: //div[contains(@class, 'hotel-card') and .//h5[contains(@class, 'card-title') and contains(text(), 'Rose Boutique')]]/descendant::a[contains(@class, 'custom-hl-view-btn')] (tried for 15 second(s) with 500 milliseconds interval)
+Build info: version: '4.31.0', revision: '1ef9f18787*'
+System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '21.0.8'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 150.0.7871.115, chrome: {chromedriverVersion: 150.0.7871.124 (9261fd0a595..., userDataDir: C:\Users\luuhu\AppData\Loca...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:55513}, goog:processID: 12356, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:55513/devtoo..., se:cdpVersion: 150.0.7871.115, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 1de264657b5f66b0ab3338831f795a52</t>
   </si>
 </sst>
 </file>
@@ -184,12 +204,12 @@
   <cols>
     <col min="1" max="1" width="10.84765625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="13.06640625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="37.96875" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="16.9453125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="12.55859375" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="17.046875" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="10.328125" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="6.06640625" customWidth="true" bestFit="true"/>
     <col min="7" max="7" width="17.5546875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="66.59765625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="255.0" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -234,7 +254,7 @@
       <c r="E2" t="s" s="0">
         <v>12</v>
       </c>
-      <c r="F2" t="s" s="2">
+      <c r="F2" t="s" s="3">
         <v>13</v>
       </c>
       <c r="G2" t="s" s="0">
@@ -260,7 +280,7 @@
       <c r="E3" t="s" s="0">
         <v>12</v>
       </c>
-      <c r="F3" t="s" s="2">
+      <c r="F3" t="s" s="3">
         <v>13</v>
       </c>
       <c r="G3" t="s" s="0">
@@ -286,7 +306,7 @@
       <c r="E4" t="s" s="0">
         <v>12</v>
       </c>
-      <c r="F4" t="s" s="2">
+      <c r="F4" t="s" s="3">
         <v>13</v>
       </c>
       <c r="G4" t="s" s="0">
@@ -312,7 +332,7 @@
       <c r="E5" t="s" s="0">
         <v>12</v>
       </c>
-      <c r="F5" t="s" s="2">
+      <c r="F5" t="s" s="3">
         <v>13</v>
       </c>
       <c r="G5" t="s" s="0">
